--- a/artfynd/A 15258-2025 artfynd.xlsx
+++ b/artfynd/A 15258-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123750955</v>
       </c>
       <c r="B2" t="n">
-        <v>56697</v>
+        <v>56700</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>123741449</v>
       </c>
       <c r="B3" t="n">
-        <v>56689</v>
+        <v>56692</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>123750283</v>
       </c>
       <c r="B4" t="n">
-        <v>57640</v>
+        <v>57643</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 15258-2025 artfynd.xlsx
+++ b/artfynd/A 15258-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123750955</v>
+        <v>123741449</v>
       </c>
       <c r="B2" t="n">
-        <v>56700</v>
+        <v>56692</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,28 +687,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>102612</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>adult</t>
@@ -716,24 +720,29 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>i par</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sjöäng, Sjöäng, Vrm</t>
+          <t>Lilla Kroktjärn, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478065</v>
+        <v>478078</v>
       </c>
       <c r="R2" t="n">
-        <v>6586558</v>
+        <v>6586586</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,22 +769,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:52</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:52</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,22 +789,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123741449</v>
+        <v>123750283</v>
       </c>
       <c r="B3" t="n">
-        <v>56692</v>
+        <v>57644</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,21 +817,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -855,21 +854,17 @@
           <t>par i lämplig häckbiotop</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lilla Kroktjärn, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478078</v>
+        <v>477985</v>
       </c>
       <c r="R3" t="n">
-        <v>6586586</v>
+        <v>6586596</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -896,12 +891,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,22 +921,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Nils Nygren</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Nils Nygren</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123750283</v>
+        <v>123750955</v>
       </c>
       <c r="B4" t="n">
-        <v>57643</v>
+        <v>56700</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -940,32 +945,28 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>adult</t>
@@ -973,25 +974,24 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>i par</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lilla Kroktjärn, Vrm</t>
+          <t>Sjöäng, Sjöäng, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477985</v>
+        <v>478065</v>
       </c>
       <c r="R4" t="n">
-        <v>6586596</v>
+        <v>6586558</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 15258-2025 artfynd.xlsx
+++ b/artfynd/A 15258-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123741449</v>
+        <v>123750283</v>
       </c>
       <c r="B2" t="n">
-        <v>56692</v>
+        <v>57644</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -728,21 +728,17 @@
           <t>par i lämplig häckbiotop</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lilla Kroktjärn, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478078</v>
+        <v>477985</v>
       </c>
       <c r="R2" t="n">
-        <v>6586586</v>
+        <v>6586596</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -769,12 +765,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,22 +795,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Nils Nygren</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Nils Nygren</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123750283</v>
+        <v>123750955</v>
       </c>
       <c r="B3" t="n">
-        <v>57644</v>
+        <v>56700</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,32 +819,28 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>adult</t>
@@ -846,25 +848,24 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>i par</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lilla Kroktjärn, Vrm</t>
+          <t>Sjöäng, Sjöäng, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477985</v>
+        <v>478065</v>
       </c>
       <c r="R3" t="n">
-        <v>6586596</v>
+        <v>6586558</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -896,7 +897,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -906,7 +907,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -933,10 +934,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123750955</v>
+        <v>123741449</v>
       </c>
       <c r="B4" t="n">
-        <v>56700</v>
+        <v>56692</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -945,28 +946,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>102612</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>adult</t>
@@ -974,24 +979,29 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>i par</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sjöäng, Sjöäng, Vrm</t>
+          <t>Lilla Kroktjärn, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478065</v>
+        <v>478078</v>
       </c>
       <c r="R4" t="n">
-        <v>6586558</v>
+        <v>6586586</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1018,22 +1028,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>12:52</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>12:52</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1048,12 +1048,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 15258-2025 artfynd.xlsx
+++ b/artfynd/A 15258-2025 artfynd.xlsx
@@ -807,10 +807,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123750955</v>
+        <v>123741449</v>
       </c>
       <c r="B3" t="n">
-        <v>56700</v>
+        <v>56692</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -819,28 +819,32 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>102612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>adult</t>
@@ -848,24 +852,29 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>i par</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sjöäng, Sjöäng, Vrm</t>
+          <t>Lilla Kroktjärn, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478065</v>
+        <v>478078</v>
       </c>
       <c r="R3" t="n">
-        <v>6586558</v>
+        <v>6586586</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,22 +901,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:52</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:52</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -922,22 +921,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123741449</v>
+        <v>123750955</v>
       </c>
       <c r="B4" t="n">
-        <v>56692</v>
+        <v>56700</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -946,32 +945,28 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>adult</t>
@@ -979,29 +974,24 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>i par</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lilla Kroktjärn, Vrm</t>
+          <t>Sjöäng, Sjöäng, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478078</v>
+        <v>478065</v>
       </c>
       <c r="R4" t="n">
-        <v>6586586</v>
+        <v>6586558</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1028,12 +1018,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1048,12 +1048,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Nils Nygren</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Nils Nygren</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
